--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260608.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260608.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>161,765</t>
+          <t>157,415</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.73%</t>
+          <t>27.33%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>117,460</t>
+          <t>114,250</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.75%</t>
+          <t>10.59%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>18,435</t>
+          <t>17,955</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.37%</t>
+          <t>7.34%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>59,655</t>
+          <t>58,105</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.73%</t>
+          <t>7.34%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>142,195</t>
+          <t>138,595</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.09%</t>
         </is>
       </c>
     </row>
@@ -721,210 +721,210 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>69,830</t>
+          <t>67,920</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>231,790,402</t>
+          <t>6,535</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,715</t>
+          <t>74,715</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>76,815</t>
+          <t>51,605</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>53,055</t>
+          <t>22,535</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>23,165</t>
+          <t>20,873</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>21,463</t>
+          <t>36,020</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>37,030</t>
+          <t>87,915</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>90,385</t>
+          <t>23,175</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>23,825</t>
+          <t>125,391,714</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>60,065</t>
+          <t>58,425</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>31,228</t>
+          <t>30,378</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>22,920</t>
+          <t>22,290</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1007,78 +1007,78 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>42,560</t>
+          <t>41,400</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>69,818</t>
+          <t>9,140</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>13,731</t>
+          <t>67,908</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>9,400</t>
+          <t>13,361</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1095,51 +1095,51 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>25,098</t>
+          <t>24,408</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>149,115</t>
+          <t>11,016</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,705</t>
+          <t>145,045</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,22 +1151,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>11,326</t>
+          <t>21,115</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>23,177</t>
+          <t>22,547</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>18,721</t>
+          <t>18,211</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>44,150</t>
+          <t>42,940</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>50,760</t>
+          <t>49,370</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,56 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,845</t>
+          <t>13,465</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>211,974,600</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>6,235,615</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
